--- a/jpcore-r4b/develop/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-documentreference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -271,17 +271,17 @@
 </t>
   </si>
   <si>
-    <t>A reference to a document</t>
-  </si>
-  <si>
-    <t>A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
-  </si>
-  <si>
-    <t>Usually, this is used for documents other than those defined by FHIR.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>ドキュメントへの参照 / A reference to a document</t>
+  </si>
+  <si>
+    <t>あらゆる目的のためのあらゆる種類の文書への参照。ドキュメントを検出および管理できるように、ドキュメントに関するMetadataを提供します。ドキュメントの範囲は、MIMEタイプを備えたセラル化オブジェクトであるため、正式な患者中心のドキュメント（CDA）、Cliical Notes、スキャンされた論文、およびポリシーテキストなどの非患者固有の文書が含まれています。 / A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
+  </si>
+  <si>
+    <t>通常、これはFHIRによって定義されたもの以外のドキュメントに使用されます。 / Usually, this is used for documents other than those defined by FHIR.</t>
+  </si>
+  <si>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -312,13 +312,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -331,26 +331,26 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
     <t>DocumentReference.meta.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -370,13 +370,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -392,23 +392,27 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>DocumentReference.meta.versionId</t>
   </si>
   <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi) / Version specific identifier</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。 / The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。 / The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
   </si>
   <si>
     <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>DocumentReference.meta.lastUpdated</t>
@@ -418,13 +422,13 @@
 </t>
   </si>
   <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
+    <t>リソースのバージョンが最後に変更されたとき / When the resource version last changed</t>
+  </si>
+  <si>
+    <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。 / When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>この値はリソースが初めて作成される場合を除いて常に設定されています。サーバー/リソースマネージャーがこの値を設定します。クライアントが提供する値は関係ありません。これはHTTP Last-Modifiedに相当し、[read](http://hl7.org/fhir/R4B/http.html#read)のインタラクションで同じ値を持つべきです。 / This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
   </si>
   <si>
     <t>Meta.lastUpdated</t>
@@ -437,13 +441,14 @@
 </t>
   </si>
   <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+    <t>リソースがどこから来たかを特定する / Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。 / A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。 / In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
 This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
   </si>
   <si>
@@ -457,13 +462,13 @@
 </t>
   </si>
   <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+    <t>このリソースが適合を主張するプロファイル / Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>このリソースが準拠すると主張する [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) リソースに関するプロファイルのリストです。URL は [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url) への参照です。 / A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>これらの主張が時間の経過に伴って検証または更新される方法と、それらを決定するサーバーや他の基盤に任されます。プロファイルURLのリストは1セットです。 / It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
     <t>Meta.profile</t>
@@ -476,13 +481,13 @@
 </t>
   </si>
   <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたセキュリティラベル / Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースにはセキュリティラベルが適用されています。これらのタグにより、特定のリソースが全体的なセキュリティポリシーやインフラストラクチャに関連付けられます。 / Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>セキュリティラベルは変更せずにリソースのバージョンを更新可能です。セキュリティラベルのリストはセットであり、一意性はシステム/コードに基づき、バージョンと表示は無視されます。 / The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -497,13 +502,13 @@
     <t>DocumentReference.meta.tag</t>
   </si>
   <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたタグ / Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースに適用されるタグです。タグは、リソースをプロセスやワークフローに識別し、関連付けるために使用することが意図されており、アプリケーションはリソースの意味を解釈する際にタグを考慮する必要はありません。 / Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。 / The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>example</t>
@@ -518,13 +523,13 @@
     <t>DocumentReference.implicitRules</t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -537,19 +542,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -569,13 +574,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -595,19 +600,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -617,23 +622,34 @@
     <t>DocumentReference.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>DocumentReference.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -646,16 +662,16 @@
 </t>
   </si>
   <si>
-    <t>Master Version Specific Identifier</t>
-  </si>
-  <si>
-    <t>Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
-  </si>
-  <si>
-    <t>CDA Document Id extension and root.</t>
-  </si>
-  <si>
-    <t>The structure and format of this Id shall be consistent with the specification corresponding to the formatCode attribute. (e.g. for a DICOM standard document a 64-character numeric UID, for an HL7 CDA format a serialization of the CDA Document Id extension and root in the form "oid^extension", where OID is a 64 digits max, and the Id is a 16 UTF-8 char max. If the OID is coded without the extension then the '^' character shall not be included.).</t>
+    <t>マスターバージョン固有のidentifier / Master Version Specific Identifier</t>
+  </si>
+  <si>
+    <t>ドキュメントのソースによって割り当てられたドキュメントidentifier。このidentifierは、このバージョンのドキュメントに固有です。この一意のidentifierは、このバージョンのドキュメントを識別するために他の場所で使用できます。 / Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
+  </si>
+  <si>
+    <t>CDAドキュメントID拡張機能とルート。 / CDA Document Id extension and root.</t>
+  </si>
+  <si>
+    <t>このIDの構造と形式は、フォーマットコード属性に対応する仕様と一致するものとします。（たとえば、DICOM標準ドキュメントの場合、64文字の数値UID、HL7 CDA形式の場合、CDAドキュメントID拡張機能のシリアル化と「oid^拡張機能」の形式のルート。16 UTF-8 charmax。oidが拡張機能なしでコーディングされている場合、 '^'文字は含まれません。）。 / The structure and format of this Id shall be consistent with the specification corresponding to the formatCode attribute. (e.g. for a DICOM standard document a 64-character numeric UID, for an HL7 CDA format a serialization of the CDA Document Id extension and root in the form "oid^extension", where OID is a 64 digits max, and the Id is a 16 UTF-8 char max. If the OID is coded without the extension then the '^' character shall not be included.).</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -682,10 +698,10 @@
     <t>DocumentReference.identifier</t>
   </si>
   <si>
-    <t>Other identifiers for the document</t>
-  </si>
-  <si>
-    <t>Other identifiers associated with the document, including version independent identifiers.</t>
+    <t>ドキュメントの他のidentifier / Other identifiers for the document</t>
+  </si>
+  <si>
+    <t>バージョンの独立identifierを含む、ドキュメントに関連付けられた他のidentifier。 / Other identifiers associated with the document, including version independent identifiers.</t>
   </si>
   <si>
     <t>.id / .setId</t>
@@ -700,20 +716,21 @@
     <t>DocumentReference.status</t>
   </si>
   <si>
-    <t>current | superseded | entered-in-error</t>
-  </si>
-  <si>
-    <t>The status of this document reference.</t>
-  </si>
-  <si>
-    <t>This is the status of the DocumentReference object, which might be independent from the docStatus element.
+    <t>電流|スーパー付き|エラー入力 / current | superseded | entered-in-error</t>
+  </si>
+  <si>
+    <t>このドキュメント参照のステータス。 / The status of this document reference.</t>
+  </si>
+  <si>
+    <t>これは、DoctSatus要素から独立している可能性のあるDocumentReferenceオブジェクトのステータスです。
+この要素には、ステータスにドキュメントまたは参照を現在有効ではないとマークするコードが含まれているため、修飾子としてラベル付けされています。 / This is the status of the DocumentReference object, which might be independent from the docStatus element.
 This element is labeled as a modifier because the status contains the codes that mark the document or reference as not currently valid.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>The status of the document reference.</t>
+    <t>ドキュメント参照のステータス。 / The status of the document reference.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/document-reference-status|4.3.0</t>
@@ -737,16 +754,16 @@
     <t>DocumentReference.docStatus</t>
   </si>
   <si>
-    <t>preliminary | final | amended | entered-in-error</t>
-  </si>
-  <si>
-    <t>The status of the underlying document.</t>
-  </si>
-  <si>
-    <t>The document that is pointed to might be in various lifecycle states.</t>
-  </si>
-  <si>
-    <t>Status of the underlying document.</t>
+    <t>予備|ファイナル|修正|エラー入力 / preliminary | final | amended | entered-in-error</t>
+  </si>
+  <si>
+    <t>基礎となる文書のステータス。 / The status of the underlying document.</t>
+  </si>
+  <si>
+    <t>指摘されている文書は、さまざまなライフサイクル状態にある可能性があります。 / The document that is pointed to might be in various lifecycle states.</t>
+  </si>
+  <si>
+    <t>基礎となる文書のステータス。 / Status of the underlying document.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/composition-status|4.3.0</t>
@@ -768,16 +785,16 @@
 </t>
   </si>
   <si>
-    <t>Kind of document (LOINC if possible)</t>
-  </si>
-  <si>
-    <t>Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
-  </si>
-  <si>
-    <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
-  </si>
-  <si>
-    <t>Precise type of clinical document.</t>
+    <t>ドキュメントの種類（可能であればLoinc） / Kind of document (LOINC if possible)</t>
+  </si>
+  <si>
+    <t>参照されている特定の種類のドキュメントを指定します（例：履歴と物理的、排出概要、進行状況ノート）。これは通常、文書を参照する目的に相当します。 / Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
+  </si>
+  <si>
+    <t>彼が正確なタイプのドキュメントを説明するドキュメントを説明する重要なMetadata要素。ドキュメントのリストを表示する際に、人間がドキュメントが興味深いかどうかを評価するのに役立ちます。 / Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
+  </si>
+  <si>
+    <t>正確なタイプの臨床文書。 / Precise type of clinical document.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/doc-typecodes|4.3.0</t>
@@ -812,16 +829,16 @@
 </t>
   </si>
   <si>
-    <t>Categorization of document</t>
-  </si>
-  <si>
-    <t>A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
-  </si>
-  <si>
-    <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
-  </si>
-  <si>
-    <t>High-level kind of a clinical document at a macro level.</t>
+    <t>ドキュメントの分類 / Categorization of document</t>
+  </si>
+  <si>
+    <t>参照されるドキュメントのタイプの分類 - インデックス作成と検索に役立ちます。これは、documentreference.typeで指定されたコードによって暗示または導出される場合があります。 / A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
+  </si>
+  <si>
+    <t>ドキュメントのカテゴリまたは分類を説明する重要なMetadata要素。これは、使用方法に基づいて同様のドキュメントをグループ化するより広範な視点です。これは、検索に使用される主要なキーです。 / Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
+  </si>
+  <si>
+    <t>マクロレベルでの高レベルの臨床文書。 / High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/doc-classcodes|4.3.0</t>
@@ -846,10 +863,10 @@
 </t>
   </si>
   <si>
-    <t>Who/what is the subject of the document</t>
-  </si>
-  <si>
-    <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
+    <t>誰/文書の主題は何ですか / Who/what is the subject of the document</t>
+  </si>
+  <si>
+    <t>文書は誰または何であるか。この文書は、人、患者または医療従事者）、デバイス（機械など）、または被験者のグループ（家畜の群れに関する文書、または一般的な暴露を共有する患者のセットに関するものです。）。 / Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -880,13 +897,13 @@
 </t>
   </si>
   <si>
-    <t>When this document reference was created</t>
-  </si>
-  <si>
-    <t>When the document reference was created.</t>
-  </si>
-  <si>
-    <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
+    <t>このドキュメント参照が作成されたとき / When this document reference was created</t>
+  </si>
+  <si>
+    <t>ドキュメント参照が作成されたとき。 / When the document reference was created.</t>
+  </si>
+  <si>
+    <t>参照/インデックス作成時間は、追跡、バージョンの整理、検索に使用されます。 / Referencing/indexing time is used for tracking, organizing versions and searching.</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -908,13 +925,13 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what authored the document</t>
-  </si>
-  <si>
-    <t>Identifies who is responsible for adding the information to the document.</t>
-  </si>
-  <si>
-    <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
+    <t>誰と/または何が文書を作成したか / Who and/or what authored the document</t>
+  </si>
+  <si>
+    <t>情報をドキュメントに追加する責任者を特定します。 / Identifies who is responsible for adding the information to the document.</t>
+  </si>
+  <si>
+    <t>必ずしも実際のデータ入力（つまり、タイピスト）やソース（情報提供者）を誰が行ったのか（情報提供者）。 / Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -942,13 +959,13 @@
 </t>
   </si>
   <si>
-    <t>Who/what authenticated the document</t>
-  </si>
-  <si>
-    <t>Which person or organization authenticates that this document is valid.</t>
-  </si>
-  <si>
-    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
+    <t>誰/何がドキュメントを認証したのか / Who/what authenticated the document</t>
+  </si>
+  <si>
+    <t>どの個人または組織がこのドキュメントが有効であることを認証しています。 / Which person or organization authenticates that this document is valid.</t>
+  </si>
+  <si>
+    <t>法的に認証または証明した著者機関内の参加者を表します。法的認証は、文書が法的認証者によって手動または電子的に署名されたことを意味します。 / Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
   </si>
   <si>
     <t>Composition.attester</t>
@@ -976,13 +993,13 @@
 </t>
   </si>
   <si>
-    <t>Organization which maintains the document</t>
-  </si>
-  <si>
-    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
-  </si>
-  <si>
-    <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
+    <t>ドキュメントを維持する組織 / Organization which maintains the document</t>
+  </si>
+  <si>
+    <t>ドキュメントの継続的なメンテナンスとアクセスを担当する組織またはグループを特定します。 / Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+  </si>
+  <si>
+    <t>論理組織（ソフトウェアシステム、ベンダー、または部門）を識別して、現在のバージョン、問題などを報告する場所を見つけます。これは、ドキュメントの物理的な場所（URL、ディスクドライブ、またはサーバー）とは異なります。ホストが他の組織の管理に委任される可能性があるドキュメントの技術的な場所。 / Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
   </si>
   <si>
     <t>Composition.custodian</t>
@@ -998,16 +1015,16 @@
 </t>
   </si>
   <si>
-    <t>Relationships to other documents</t>
-  </si>
-  <si>
-    <t>Relationships that this document has with other document references that already exist.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>他のドキュメントとの関係 / Relationships to other documents</t>
+  </si>
+  <si>
+    <t>このドキュメントが既に存在する他のドキュメント参照との関係。 / Relationships that this document has with other document references that already exist.</t>
+  </si>
+  <si>
+    <t>この要素は、他のドキュメントに追加されたドキュメントが独自に不完全であるため、修飾子としてラベル付けされています。 / This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1027,7 +1044,16 @@
 </t>
   </si>
   <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>DocumentReference.relatesTo.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo.modifierExtension</t>
@@ -1037,10 +1063,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1050,16 +1077,16 @@
     <t>DocumentReference.relatesTo.code</t>
   </si>
   <si>
-    <t>replaces | transforms | signs | appends</t>
-  </si>
-  <si>
-    <t>The type of relationship that this document has with anther document.</t>
-  </si>
-  <si>
-    <t>If this document appends another document, then the document cannot be fully understood without also accessing the referenced document.</t>
-  </si>
-  <si>
-    <t>The type of relationship between documents.</t>
+    <t>交換|変換|サイン|追加 / replaces | transforms | signs | appends</t>
+  </si>
+  <si>
+    <t>このドキュメントが別のドキュメントと一緒に持っている関係のタイプ。 / The type of relationship that this document has with anther document.</t>
+  </si>
+  <si>
+    <t>このドキュメントが別のドキュメントを追加した場合、参照されるドキュメントにもアクセスせずにドキュメントを完全に理解することはできません。 / If this document appends another document, then the document cannot be fully understood without also accessing the referenced document.</t>
+  </si>
+  <si>
+    <t>ドキュメント間の関係のタイプ。 / The type of relationship between documents.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/document-relationship-type|4.3.0</t>
@@ -1081,10 +1108,10 @@
 </t>
   </si>
   <si>
-    <t>Target of the relationship</t>
-  </si>
-  <si>
-    <t>The target document of this relationship.</t>
+    <t>関係のターゲット / Target of the relationship</t>
+  </si>
+  <si>
+    <t>この関係のターゲット文書。 / The target document of this relationship.</t>
   </si>
   <si>
     <t>Composition.relatesTo.target</t>
@@ -1099,16 +1126,16 @@
     <t>DocumentReference.description</t>
   </si>
   <si>
-    <t>Human-readable description</t>
-  </si>
-  <si>
-    <t>Human-readable description of the source document.</t>
-  </si>
-  <si>
-    <t>What the document is about,  a terse summary of the document.</t>
-  </si>
-  <si>
-    <t>Helps humans to assess whether the document is of interest.</t>
+    <t>人間読み取り可能な説明 / Human-readable description</t>
+  </si>
+  <si>
+    <t>ソースドキュメントの人間の読み取り可能な説明。 / Human-readable description of the source document.</t>
+  </si>
+  <si>
+    <t>ドキュメントとは何か、ドキュメントの簡潔な要約。 / What the document is about,  a terse summary of the document.</t>
+  </si>
+  <si>
+    <t>人間が文書が興味深いかどうかを評価するのに役立ちます。 / Helps humans to assess whether the document is of interest.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="SUBJ"].target.text</t>
@@ -1123,20 +1150,21 @@
     <t>DocumentReference.securityLabel</t>
   </si>
   <si>
-    <t>Document security-tags</t>
-  </si>
-  <si>
-    <t>A set of Security-Tag codes specifying the level of privacy/security of the Document. Note that DocumentReference.meta.security contains the security labels of the "reference" to the document, while DocumentReference.securityLabel contains a snapshot of the security labels on the document the reference refers to.</t>
-  </si>
-  <si>
-    <t>The confidentiality codes can carry multiple vocabulary items. HL7 has developed an understanding of security and privacy tags that might be desirable in a Document Sharing environment, called HL7 Healthcare Privacy and Security Classification System (HCS). The following specification is recommended but not mandated, as the vocabulary bindings are an administrative domain responsibility. The use of this method is up to the policy domain such as the XDS Affinity Domain or other Trust Domain where all parties including sender and recipients are trusted to appropriately tag and enforce.   
+    <t>ドキュメントセキュリティタグ / Document security-tags</t>
+  </si>
+  <si>
+    <t>ドキュメントのプライバシー/セキュリティのレベルを指定するセキュリティタグコードのセット。documentreference.meta.securityにはドキュメントへの「参照」のセキュリティラベルが含まれていることに注意してください。一方、documentReference.securityLabelには、参照が参照するドキュメント上のセキュリティラベルのスナップショットが含まれています。 / A set of Security-Tag codes specifying the level of privacy/security of the Document. Note that DocumentReference.meta.security contains the security labels of the "reference" to the document, while DocumentReference.securityLabel contains a snapshot of the security labels on the document the reference refers to.</t>
+  </si>
+  <si>
+    <t>機密性コードには、複数の語彙項目を搭載できます。HL7は、HL7ヘルスケアプライバシーとセキュリティ分類システム（HCS）と呼ばれるドキュメント共有環境で望ましいセキュリティとプライバシータグの理解を開発しました。語彙のバインディングは管理領域の責任であるため、次の仕様が推奨されますが、義務付けられていません。この方法の使用は、送信者や受信者を含むすべての関係者が適切にタグ付けおよび執行すると信頼されているXDSアフィニティドメインやその他の信頼ドメインなどのポリシードメイン次第です。
+HL7ヘルスケアのプライバシーとセキュリティ分類（HCS）には、機密性、感度、完全性、および取り扱い警告に固有のコードシステムがあります。いくつかの価値は、ワークフローの役割と特別なプロジェクトに関連しているため、ローカルの語彙から得られます。 / The confidentiality codes can carry multiple vocabulary items. HL7 has developed an understanding of security and privacy tags that might be desirable in a Document Sharing environment, called HL7 Healthcare Privacy and Security Classification System (HCS). The following specification is recommended but not mandated, as the vocabulary bindings are an administrative domain responsibility. The use of this method is up to the policy domain such as the XDS Affinity Domain or other Trust Domain where all parties including sender and recipients are trusted to appropriately tag and enforce.   
 In the HL7 Healthcare Privacy and Security Classification (HCS) there are code systems specific to Confidentiality, Sensitivity, Integrity, and Handling Caveats. Some values would come from a local vocabulary as they are related to workflow roles and special projects.</t>
   </si>
   <si>
-    <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+    <t>ヘルスケアプライバシー/セキュリティ分類（HCS）セキュリティタグの使用システムの使用が推奨されます。 / Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
+  </si>
+  <si>
+    <t>ヘルスケアプライバシーとセキュリティ分類システムからのセキュリティラベル。 / Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1157,10 +1185,10 @@
     <t>DocumentReference.content</t>
   </si>
   <si>
-    <t>Document referenced</t>
-  </si>
-  <si>
-    <t>The document and format referenced. There may be multiple content element repetitions, each with a different format.</t>
+    <t>参照されたドキュメント / Document referenced</t>
+  </si>
+  <si>
+    <t>参照されたドキュメントとフォーマット。複数のコンテンツ要素の繰り返しがあり、それぞれが異なる形式を備えている場合があります。 / The document and format referenced. There may be multiple content element repetitions, each with a different format.</t>
   </si>
   <si>
     <t>Bundle(Composition+*)</t>
@@ -1185,10 +1213,10 @@
 </t>
   </si>
   <si>
-    <t>Where to access the document</t>
-  </si>
-  <si>
-    <t>The document or URL of the document along with critical metadata to prove content has integrity.</t>
+    <t>ドキュメントにアクセスする場所 / Where to access the document</t>
+  </si>
+  <si>
+    <t>ドキュメントのドキュメントまたはURLと、コンテンツに整合性があることを証明する重要なMetadataがあります。 / The document or URL of the document along with critical metadata to prove content has integrity.</t>
   </si>
   <si>
     <t>Composition.language, 
@@ -1208,16 +1236,16 @@
     <t>DocumentReference.content.format</t>
   </si>
   <si>
-    <t>Format/content rules for the document</t>
-  </si>
-  <si>
-    <t>An identifier of the document encoding, structure, and template that the document conforms to beyond the base format indicated in the mimeType.</t>
-  </si>
-  <si>
-    <t>Note that while IHE mostly issues URNs for format types, not all documents can be identified by a URI.</t>
-  </si>
-  <si>
-    <t>Document Format Codes.</t>
+    <t>ドキュメントのフォーマット/コンテンツルール / Format/content rules for the document</t>
+  </si>
+  <si>
+    <t>ドキュメントがエンコード、構造、およびテンプレートのidentifierは、ドキュメントがMIMETYPEに示されているベース形式を超えて適合することです。 / An identifier of the document encoding, structure, and template that the document conforms to beyond the base format indicated in the mimeType.</t>
+  </si>
+  <si>
+    <t>iheは主にフォーマットタイプのurnsを発行しますが、すべてのドキュメントがURIで識別できるわけではないことに注意してください。 / Note that while IHE mostly issues URNs for format types, not all documents can be identified by a URI.</t>
+  </si>
+  <si>
+    <t>ドキュメント形式コード。 / Document Format Codes.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/formatcodes|4.3.0</t>
@@ -1235,13 +1263,13 @@
     <t>DocumentReference.context</t>
   </si>
   <si>
-    <t>Clinical context of document</t>
-  </si>
-  <si>
-    <t>The clinical context in which the document was prepared.</t>
-  </si>
-  <si>
-    <t>These values are primarily added to help with searching for interesting/relevant documents.</t>
+    <t>文書の臨床コンテキスト / Clinical context of document</t>
+  </si>
+  <si>
+    <t>文書が準備された臨床コンテキスト。 / The clinical context in which the document was prepared.</t>
+  </si>
+  <si>
+    <t>これらの値は、主に興味深い/関連するドキュメントの検索に役立つために追加されます。 / These values are primarily added to help with searching for interesting/relevant documents.</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode="SUBJ"].target[classCode&lt;'ACT']</t>
@@ -1263,10 +1291,10 @@
 </t>
   </si>
   <si>
-    <t>Context of the document  content</t>
-  </si>
-  <si>
-    <t>Describes the clinical encounter or type of care that the document content is associated with.</t>
+    <t>ドキュメントコンテンツのコンテキスト / Context of the document  content</t>
+  </si>
+  <si>
+    <t>ドキュメントコンテンツが関連付けられている臨床的Enounterまたはケアの種類について説明します。 / Describes the clinical encounter or type of care that the document content is associated with.</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1284,16 +1312,16 @@
     <t>DocumentReference.context.event</t>
   </si>
   <si>
-    <t>Main clinical acts documented</t>
-  </si>
-  <si>
-    <t>This list of codes represents the main clinical acts, such as a colonoscopy or an appendectomy, being documented. In some cases, the event is inherent in the type Code, such as a "History and Physical Report" in which the procedure being documented is necessarily a "History and Physical" act.</t>
-  </si>
-  <si>
-    <t>An event can further specialize the act inherent in the type, such as  where it is simply "Procedure Report" and the procedure was a "colonoscopy". If one or more event codes are included, they shall not conflict with the values inherent in the class or type elements as such a conflict would create an ambiguous situation.</t>
-  </si>
-  <si>
-    <t>This list of codes represents the main clinical acts being documented.</t>
+    <t>主な臨床行為が文書化されています / Main clinical acts documented</t>
+  </si>
+  <si>
+    <t>このコードのリストは、文書化されている大腸内視鏡検査や虫垂切除術などの主要な臨床行為を表しています。場合によっては、このイベントは、文書化されているプロシジャー（処置等）が必然的に「歴史と物理的」行為である「履歴と物理的報告」など、タイプコードに固有のものです。 / This list of codes represents the main clinical acts, such as a colonoscopy or an appendectomy, being documented. In some cases, the event is inherent in the type Code, such as a "History and Physical Report" in which the procedure being documented is necessarily a "History and Physical" act.</t>
+  </si>
+  <si>
+    <t>イベントは、単に「プロシジャー（処置等）報告書」であり、プロシジャー（処置等）は「大腸鏡検査」であるなど、タイプに固有の行為をさらに専門化することができます。1つ以上のイベントコードが含まれている場合、クラスまたはタイプの要素に固有の値と矛盾してはなりません。そのような競合が曖昧な状況を生み出すためです。 / An event can further specialize the act inherent in the type, such as  where it is simply "Procedure Report" and the procedure was a "colonoscopy". If one or more event codes are included, they shall not conflict with the values inherent in the class or type elements as such a conflict would create an ambiguous situation.</t>
+  </si>
+  <si>
+    <t>このコードのリストは、文書化されている主要な臨床行為を表しています。 / This list of codes represents the main clinical acts being documented.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
@@ -1315,10 +1343,10 @@
 </t>
   </si>
   <si>
-    <t>Time of service that is being documented</t>
-  </si>
-  <si>
-    <t>The time period over which the service that is described by the document was provided.</t>
+    <t>文書化されているサービス時間 / Time of service that is being documented</t>
+  </si>
+  <si>
+    <t>ドキュメントで説明されているサービスが提供された期間。 / The time period over which the service that is described by the document was provided.</t>
   </si>
   <si>
     <t>Composition.event.period</t>
@@ -1340,13 +1368,13 @@
     <t>DocumentReference.context.facilityType</t>
   </si>
   <si>
-    <t>Kind of facility where patient was seen</t>
-  </si>
-  <si>
-    <t>The kind of facility where the patient was seen.</t>
-  </si>
-  <si>
-    <t>XDS Facility Type.</t>
+    <t>患者が見られたような施設 / Kind of facility where patient was seen</t>
+  </si>
+  <si>
+    <t>患者が見られた施設の種類。 / The kind of facility where the patient was seen.</t>
+  </si>
+  <si>
+    <t>XDS施設タイプ。 / XDS Facility Type.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes|4.3.0</t>
@@ -1367,19 +1395,19 @@
     <t>DocumentReference.context.practiceSetting</t>
   </si>
   <si>
-    <t>Additional details about where the content was created (e.g. clinical specialty)</t>
-  </si>
-  <si>
-    <t>This property may convey specifics about the practice setting where the content was created, often reflecting the clinical specialty.</t>
-  </si>
-  <si>
-    <t>This element should be based on a coarse classification system for the class of specialty practice. Recommend the use of the classification system for Practice Setting, such as that described by the Subject Matter Domain in LOINC.</t>
-  </si>
-  <si>
-    <t>This is an important piece of metadata that providers often rely upon to quickly sort and/or filter out to find specific content.</t>
-  </si>
-  <si>
-    <t>Additional details about where the content was created (e.g. clinical specialty).</t>
+    <t>コンテンツが作成された場所に関する追加の詳細（臨床専門分野など） / Additional details about where the content was created (e.g. clinical specialty)</t>
+  </si>
+  <si>
+    <t>このプロパティは、コンテンツが作成された練習設定に関する詳細を伝える場合があり、多くの場合、臨床の専門性を反映しています。 / This property may convey specifics about the practice setting where the content was created, often reflecting the clinical specialty.</t>
+  </si>
+  <si>
+    <t>この要素は、専門診療のクラスのための粗い分類システムに基づいている必要があります。LOINCの主題ドメインによって記述されているような練習設定に分類システムの使用を推奨します。 / This element should be based on a coarse classification system for the class of specialty practice. Recommend the use of the classification system for Practice Setting, such as that described by the Subject Matter Domain in LOINC.</t>
+  </si>
+  <si>
+    <t>これは、プロバイダーがしばしば迅速にソートおよび/または除外して特定のコンテンツを見つけるために依存する重要なMetadataです。 / This is an important piece of metadata that providers often rely upon to quickly sort and/or filter out to find specific content.</t>
+  </si>
+  <si>
+    <t>コンテンツが作成された場所に関する追加の詳細（臨床専門分野など）。 / Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.3.0</t>
@@ -1395,10 +1423,10 @@
 </t>
   </si>
   <si>
-    <t>Patient demographics from source</t>
-  </si>
-  <si>
-    <t>The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>
+    <t>ソースからの患者の属性情報 / Patient demographics from source</t>
+  </si>
+  <si>
+    <t>ドキュメントが公開されたときに既知の患者情報。特定のバージョンへの参照、または含まれる場合があります。 / The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>
   </si>
   <si>
     <t>DocumentEntry.sourcePatientInfo, DocumentEntry.sourcePatientId</t>
@@ -1411,13 +1439,13 @@
 </t>
   </si>
   <si>
-    <t>Related identifiers or resources</t>
-  </si>
-  <si>
-    <t>Related identifiers or resources associated with the DocumentReference.</t>
-  </si>
-  <si>
-    <t>May be identifiers or resources that caused the DocumentReference or referenced Document to be created.</t>
+    <t>関連するidentifierまたはリソース / Related identifiers or resources</t>
+  </si>
+  <si>
+    <t>ドキュメントレファレンスに関連する関連identifierまたはリソース。 / Related identifiers or resources associated with the DocumentReference.</t>
+  </si>
+  <si>
+    <t>ドキュメントレファレンスまたは参照されたドキュメントを作成したidentifierまたはリソースが作成される場合があります。 / May be identifiers or resources that caused the DocumentReference or referenced Document to be created.</t>
   </si>
   <si>
     <t>Composition.event.detail</t>
@@ -1773,7 +1801,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.66796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="100.09765625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="48.8671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2634,7 +2662,7 @@
         <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
@@ -2660,10 +2688,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2686,16 +2714,16 @@
         <v>95</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2745,7 +2773,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
@@ -2757,7 +2785,7 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
@@ -2783,10 +2811,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2809,16 +2837,16 @@
         <v>95</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2868,7 +2896,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -2880,7 +2908,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -2906,10 +2934,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2932,16 +2960,16 @@
         <v>95</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2991,7 +3019,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -3003,7 +3031,7 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -3029,10 +3057,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3055,16 +3083,16 @@
         <v>95</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3090,11 +3118,11 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3112,7 +3140,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3124,7 +3152,7 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -3150,10 +3178,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3176,16 +3204,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3211,11 +3239,11 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3233,7 +3261,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3245,7 +3273,7 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
@@ -3271,10 +3299,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3297,16 +3325,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3356,7 +3384,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3394,10 +3422,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3420,16 +3448,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3455,13 +3483,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3479,7 +3507,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3517,14 +3545,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3543,16 +3571,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3602,7 +3630,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3623,7 +3651,7 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -3640,14 +3668,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3666,16 +3694,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3725,7 +3753,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3737,7 +3765,7 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -3746,7 +3774,7 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -3763,10 +3791,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3792,13 +3820,13 @@
         <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3848,7 +3876,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3860,7 +3888,7 @@
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
@@ -3869,7 +3897,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -3886,10 +3914,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3915,16 +3943,16 @@
         <v>114</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>117</v>
-      </c>
       <c r="O18" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3973,7 +4001,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3985,7 +4013,7 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -3994,7 +4022,7 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
@@ -4011,10 +4039,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4037,19 +4065,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4098,7 +4126,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4113,33 +4141,33 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4162,13 +4190,13 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4219,7 +4247,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4234,33 +4262,33 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4283,16 +4311,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4318,31 +4346,31 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>94</v>
@@ -4357,33 +4385,33 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4406,16 +4434,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4441,31 +4469,31 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4483,19 +4511,19 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>80</v>
@@ -4503,10 +4531,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4529,16 +4557,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4564,13 +4592,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4588,7 +4616,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4603,37 +4631,37 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4652,16 +4680,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4687,13 +4715,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -4711,7 +4739,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4729,30 +4757,30 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4775,13 +4803,13 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4832,7 +4860,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4847,37 +4875,37 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4896,16 +4924,16 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4955,7 +4983,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4970,19 +4998,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -4993,10 +5021,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5019,16 +5047,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5078,7 +5106,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5093,33 +5121,33 @@
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5142,16 +5170,16 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5201,7 +5229,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5216,33 +5244,33 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5265,16 +5293,16 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5324,7 +5352,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5339,13 +5367,13 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5362,10 +5390,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5388,16 +5416,16 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5447,7 +5475,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5459,16 +5487,16 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5480,15 +5508,15 @@
         <v>80</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5511,13 +5539,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>108</v>
+        <v>329</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
+        <v>330</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5606,10 +5634,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5635,13 +5663,13 @@
         <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5703,7 +5731,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
@@ -5729,14 +5757,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5758,16 +5786,16 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5816,7 +5844,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5828,7 +5856,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5837,7 +5865,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5854,10 +5882,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5880,16 +5908,16 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5915,13 +5943,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -5939,7 +5967,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>94</v>
@@ -5957,10 +5985,10 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5972,15 +6000,15 @@
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6003,13 +6031,13 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6060,7 +6088,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>94</v>
@@ -6078,10 +6106,10 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6093,15 +6121,15 @@
         <v>80</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6124,19 +6152,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6185,7 +6213,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6206,7 +6234,7 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6215,18 +6243,18 @@
         <v>80</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6249,19 +6277,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6286,13 +6314,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6310,7 +6338,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6328,30 +6356,30 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6374,13 +6402,13 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6431,7 +6459,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>94</v>
@@ -6443,16 +6471,16 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6469,10 +6497,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6495,13 +6523,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>329</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
+        <v>330</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6590,10 +6618,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6619,13 +6647,13 @@
         <v>114</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6687,7 +6715,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6713,14 +6741,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6742,16 +6770,16 @@
         <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6800,7 +6828,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6812,7 +6840,7 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6821,7 +6849,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -6838,10 +6866,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6864,13 +6892,13 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6921,7 +6949,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>94</v>
@@ -6939,30 +6967,30 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6985,16 +7013,16 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7020,13 +7048,13 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -7044,7 +7072,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7062,13 +7090,13 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7077,15 +7105,15 @@
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7108,16 +7136,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7167,7 +7195,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7179,7 +7207,7 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7188,7 +7216,7 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7205,10 +7233,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7231,13 +7259,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>108</v>
+        <v>329</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>109</v>
+        <v>330</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7326,10 +7354,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7355,13 +7383,13 @@
         <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7423,7 +7451,7 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7449,14 +7477,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7478,16 +7506,16 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7536,7 +7564,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7548,7 +7576,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7557,7 +7585,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7574,10 +7602,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7600,13 +7628,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7657,7 +7685,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7672,19 +7700,19 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>80</v>
@@ -7695,10 +7723,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7721,16 +7749,16 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7756,13 +7784,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7780,7 +7808,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7798,10 +7826,10 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -7813,15 +7841,15 @@
         <v>80</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7844,13 +7872,13 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7901,7 +7929,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7919,13 +7947,13 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7934,15 +7962,15 @@
         <v>80</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7965,13 +7993,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7998,13 +8026,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8022,7 +8050,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8040,13 +8068,13 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8055,15 +8083,15 @@
         <v>80</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8086,19 +8114,19 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8123,13 +8151,13 @@
         <v>80</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
@@ -8147,7 +8175,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8165,13 +8193,13 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8180,15 +8208,15 @@
         <v>80</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8211,13 +8239,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8268,7 +8296,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8286,13 +8314,13 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8301,15 +8329,15 @@
         <v>80</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8332,16 +8360,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8391,7 +8419,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8409,13 +8437,13 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8424,7 +8452,7 @@
         <v>80</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
